--- a/hasil/Non-CLAHE/Run2/history.xlsx
+++ b/hasil/Non-CLAHE/Run2/history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -463,13 +463,13 @@
         <v>0.5666666626930237</v>
       </c>
       <c r="C2" t="n">
-        <v>0.6222222447395325</v>
+        <v>0.6000000238418579</v>
       </c>
       <c r="D2" t="n">
-        <v>1.099589943885803</v>
+        <v>1.042794704437256</v>
       </c>
       <c r="E2" t="n">
-        <v>1.209607362747192</v>
+        <v>0.7754237651824951</v>
       </c>
     </row>
     <row r="3">
@@ -477,16 +477,16 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>0.7190476059913635</v>
+        <v>0.7333333492279053</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6222222447395325</v>
+        <v>0.8222222328186035</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6527060270309448</v>
+        <v>0.6266972422599792</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8121365308761597</v>
+        <v>0.5304183959960938</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>0.8095238208770752</v>
+        <v>0.7666666507720947</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7333333492279053</v>
+        <v>0.8222222328186035</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4329658448696136</v>
+        <v>0.5571318864822388</v>
       </c>
       <c r="E4" t="n">
-        <v>0.6216988563537598</v>
+        <v>0.5594087243080139</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>0.8523809313774109</v>
+        <v>0.8333333134651184</v>
       </c>
       <c r="C5" t="n">
-        <v>0.800000011920929</v>
+        <v>0.7777777910232544</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3988747298717499</v>
+        <v>0.4207448661327362</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4907805919647217</v>
+        <v>0.5505578517913818</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>0.8523809313774109</v>
+        <v>0.8666666746139526</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8444444537162781</v>
+        <v>0.800000011920929</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3593251407146454</v>
+        <v>0.3659151792526245</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4592486917972565</v>
+        <v>0.5358706712722778</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>0.8571428656578064</v>
+        <v>0.8714285492897034</v>
       </c>
       <c r="C7" t="n">
-        <v>0.800000011920929</v>
+        <v>0.8666666746139526</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3752562999725342</v>
+        <v>0.3181404173374176</v>
       </c>
       <c r="E7" t="n">
-        <v>0.4996494352817535</v>
+        <v>0.4462895691394806</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>0.8666666746139526</v>
+        <v>0.8999999761581421</v>
       </c>
       <c r="C8" t="n">
-        <v>0.7555555701255798</v>
+        <v>0.8444444537162781</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3312481045722961</v>
+        <v>0.2863533794879913</v>
       </c>
       <c r="E8" t="n">
-        <v>0.5050048232078552</v>
+        <v>0.4034403562545776</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>0.9142857193946838</v>
+        <v>0.8952381014823914</v>
       </c>
       <c r="C9" t="n">
-        <v>0.800000011920929</v>
+        <v>0.7555555701255798</v>
       </c>
       <c r="D9" t="n">
-        <v>0.2770556509494781</v>
+        <v>0.2379001379013062</v>
       </c>
       <c r="E9" t="n">
-        <v>0.5019513368606567</v>
+        <v>0.4771979153156281</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>0.9428571462631226</v>
+        <v>0.9047619104385376</v>
       </c>
       <c r="C10" t="n">
-        <v>0.8444444537162781</v>
+        <v>0.800000011920929</v>
       </c>
       <c r="D10" t="n">
-        <v>0.2363236546516418</v>
+        <v>0.276421457529068</v>
       </c>
       <c r="E10" t="n">
-        <v>0.4317476451396942</v>
+        <v>0.5407130718231201</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>0.9285714030265808</v>
+        <v>0.9142857193946838</v>
       </c>
       <c r="C11" t="n">
-        <v>0.8444444537162781</v>
+        <v>0.8666666746139526</v>
       </c>
       <c r="D11" t="n">
-        <v>0.203772097826004</v>
+        <v>0.2291446179151535</v>
       </c>
       <c r="E11" t="n">
-        <v>0.4221673011779785</v>
+        <v>0.4425157308578491</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8952381014823914</v>
+        <v>0.9047619104385376</v>
       </c>
       <c r="C12" t="n">
-        <v>0.8888888955116272</v>
+        <v>0.8666666746139526</v>
       </c>
       <c r="D12" t="n">
-        <v>0.2716356515884399</v>
+        <v>0.234941840171814</v>
       </c>
       <c r="E12" t="n">
-        <v>0.3818836510181427</v>
+        <v>0.4249180257320404</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>0.9523809552192688</v>
+        <v>0.9095237851142883</v>
       </c>
       <c r="C13" t="n">
-        <v>0.8888888955116272</v>
+        <v>0.800000011920929</v>
       </c>
       <c r="D13" t="n">
-        <v>0.1828300505876541</v>
+        <v>0.2479045540094376</v>
       </c>
       <c r="E13" t="n">
-        <v>0.3669841289520264</v>
+        <v>0.4885940849781036</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>0.8999999761581421</v>
+        <v>0.9333333373069763</v>
       </c>
       <c r="C14" t="n">
-        <v>0.800000011920929</v>
+        <v>0.8222222328186035</v>
       </c>
       <c r="D14" t="n">
-        <v>0.2596246600151062</v>
+        <v>0.1830140054225922</v>
       </c>
       <c r="E14" t="n">
-        <v>0.434494286775589</v>
+        <v>0.4933440387248993</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>0.9476190209388733</v>
+        <v>0.9571428298950195</v>
       </c>
       <c r="C15" t="n">
-        <v>0.7111111283302307</v>
+        <v>0.7333333492279053</v>
       </c>
       <c r="D15" t="n">
-        <v>0.1744530647993088</v>
+        <v>0.1466138511896133</v>
       </c>
       <c r="E15" t="n">
-        <v>0.6742230653762817</v>
+        <v>0.5708812475204468</v>
       </c>
     </row>
     <row r="16">
@@ -701,13 +701,13 @@
         <v>0.9523809552192688</v>
       </c>
       <c r="C16" t="n">
-        <v>0.7111111283302307</v>
+        <v>0.8222222328186035</v>
       </c>
       <c r="D16" t="n">
-        <v>0.1620875000953674</v>
+        <v>0.1432366371154785</v>
       </c>
       <c r="E16" t="n">
-        <v>0.7028478980064392</v>
+        <v>0.4377362132072449</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,356 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9380952119827271</v>
+        <v>0.961904764175415</v>
       </c>
       <c r="C17" t="n">
+        <v>0.8888888955116272</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.1327297240495682</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.3266220092773438</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="n">
+        <v>0.9476190209388733</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.8444444537162781</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.1512429416179657</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.3448500633239746</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="n">
+        <v>0.976190447807312</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.800000011920929</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.1182809844613075</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.383645623922348</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="n">
+        <v>0.9904761910438538</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.7555555701255798</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0.07979638874530792</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.4584898948669434</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="n">
+        <v>0.9714285731315613</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.8444444537162781</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0.1137685850262642</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.4508835673332214</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="n">
+        <v>0.9571428298950195</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0.800000011920929</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0.1306968629360199</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.40325528383255</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="n">
+        <v>0.976190447807312</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0.800000011920929</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0.0952732190489769</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.3998030424118042</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="n">
+        <v>0.9952380657196045</v>
+      </c>
+      <c r="C24" t="n">
         <v>0.8222222328186035</v>
       </c>
-      <c r="D17" t="n">
-        <v>0.1906371712684631</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0.4601413607597351</v>
+      <c r="D24" t="n">
+        <v>0.08008751273155212</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.3374143540859222</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="n">
+        <v>0.9809523820877075</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.8444444537162781</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0.1031059473752975</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.3440985381603241</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="n">
+        <v>0.9809523820877075</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.9111111164093018</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0.08173083513975143</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.2679403126239777</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="n">
+        <v>0.9809523820877075</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.8888888955116272</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0.06587642431259155</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.2459540665149689</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="n">
+        <v>0.9714285731315613</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.8888888955116272</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0.1049270704388618</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.2700618803501129</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="n">
+        <v>0.9857142567634583</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.9111111164093018</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0.07990939170122147</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.3430278897285461</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="n">
+        <v>0.9809523820877075</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.8888888955116272</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0.07910468429327011</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.2991208732128143</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="n">
+        <v>0.9714285731315613</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.9111111164093018</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0.09531071037054062</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.3001237511634827</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="n">
+        <v>0.976190447807312</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.800000011920929</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0.06966327130794525</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.4588741660118103</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="n">
+        <v>0.9714285731315613</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.800000011920929</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0.077134869992733</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.5163779258728027</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="n">
+        <v>0.9666666388511658</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0.800000011920929</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0.09762447327375412</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.4160686433315277</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="n">
+        <v>0.9571428298950195</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.8888888955116272</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0.1243313401937485</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.3087291419506073</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="n">
+        <v>0.9666666388511658</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0.8444444537162781</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0.1247031837701797</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.4054601490497589</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="n">
+        <v>0.9857142567634583</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0.8666666746139526</v>
+      </c>
+      <c r="D37" t="n">
+        <v>0.07124041765928268</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.3564117848873138</v>
       </c>
     </row>
   </sheetData>
